--- a/excel-imports/student_performance.xlsx
+++ b/excel-imports/student_performance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\school-ceo-dashboard review 1\school-ceo-dashboard\excel-imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BD786C-0851-4818-BE99-4BFAC6B4583F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E5328B-17DA-4F6A-8F08-036FE7603711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Student Performance" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Name</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Low Risk (23%)</t>
   </si>
   <si>
-    <t>76%</t>
-  </si>
-  <si>
     <t>81%</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
   </si>
   <si>
     <t>93%</t>
-  </si>
-  <si>
-    <t>99%</t>
   </si>
   <si>
     <t>70%</t>
@@ -563,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -576,20 +570,20 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2" s="1">
+        <v>0.74</v>
       </c>
       <c r="E2" s="1">
         <v>0.85</v>
       </c>
       <c r="F2" s="1">
-        <v>0.97</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G2" s="1">
         <v>0.81</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1">
         <v>0.89</v>
@@ -597,28 +591,28 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.81</v>
@@ -626,28 +620,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
       </c>
       <c r="E4" s="1">
         <v>0.75</v>
       </c>
       <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1">
         <v>0.9</v>
@@ -655,28 +649,28 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
       </c>
       <c r="I5" s="1">
         <v>0.89</v>
@@ -684,28 +678,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
       </c>
       <c r="I6" s="1">
         <v>0.96</v>
@@ -713,28 +707,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
         <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -742,28 +736,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>46</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
       </c>
       <c r="I8" s="1">
         <v>0.91</v>
@@ -771,28 +765,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9" t="s">
         <v>53</v>
       </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
       </c>
       <c r="I9" s="1">
         <v>0.85</v>

--- a/excel-imports/student_performance.xlsx
+++ b/excel-imports/student_performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\school-ceo-dashboard review 1\school-ceo-dashboard\excel-imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCB8823-CC9A-419E-8287-185B0E2A3CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F52D8B4-9BFC-41B3-8F7F-728E541956E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -568,10 +568,10 @@
         <v>0.74</v>
       </c>
       <c r="E2" s="1">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="F2" s="1">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="G2" s="1">
         <v>0.85</v>
